--- a/lai/valuationquan/AIindex/AIinduindexmodel2cn.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel2cn.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -109,16 +109,12 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
+    <t>MA250</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>人工智能产业指数</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>MA250</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>绝对收益率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -719,7 +715,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1034,6 +1030,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1043,7 +1042,7 @@
               <c:f>'模型二 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -1357,6 +1356,9 @@
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>4228.3228496289457</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
               </c:numCache>
@@ -1400,7 +1402,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1715,6 +1717,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1724,7 +1729,7 @@
               <c:f>'模型二 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="1">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -2035,6 +2040,9 @@
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>5934.4066689137917</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
               </c:numCache>
@@ -2078,7 +2086,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2393,6 +2401,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2402,7 +2413,7 @@
               <c:f>'模型二 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2716,6 +2727,9 @@
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>1706.083819284846</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
               </c:numCache>
@@ -2738,11 +2752,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="467603840"/>
-        <c:axId val="467606144"/>
+        <c:axId val="316529280"/>
+        <c:axId val="403558784"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="467603840"/>
+        <c:axId val="316529280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2785,14 +2799,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467606144"/>
+        <c:crossAx val="403558784"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="467606144"/>
+        <c:axId val="403558784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2841,7 +2855,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="467603840"/>
+        <c:crossAx val="316529280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3054,7 +3068,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3333,6 +3347,9 @@
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3342,7 +3359,7 @@
               <c:f>'模型二 (1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3620,6 +3637,9 @@
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
                 <c:pt idx="92">
+                  <c:v>6898.9353000000046</c:v>
+                </c:pt>
+                <c:pt idx="93">
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
               </c:numCache>
@@ -3663,7 +3683,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3942,6 +3962,9 @@
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3951,7 +3974,7 @@
               <c:f>'模型二 (1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4205,31 +4228,34 @@
                   <c:v>9660.119413601813</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>9611.0758407035883</c:v>
+                  <c:v>9611.168879345516</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>9551.9109549018176</c:v>
+                  <c:v>9552.1546310102676</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>9593.2161315660869</c:v>
+                  <c:v>9593.318194348185</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>9643.7845563179562</c:v>
+                  <c:v>9643.614070607824</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>9655.3867910659719</c:v>
+                  <c:v>9655.027430831773</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>9655.3867910659719</c:v>
+                  <c:v>9655.027430831773</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>9655.3867910659719</c:v>
+                  <c:v>9655.027430831773</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>9655.3867910659719</c:v>
+                  <c:v>9655.027430831773</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>9655.3867910659719</c:v>
+                  <c:v>9655.027430831773</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>9655.027430831773</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4272,7 +4298,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4551,6 +4577,9 @@
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4560,7 +4589,7 @@
               <c:f>'模型二 (1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4814,31 +4843,34 @@
                   <c:v>2761.1841136018083</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>2712.1405407035836</c:v>
+                  <c:v>2712.2335793455113</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>2652.975654901813</c:v>
+                  <c:v>2653.219331010263</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>2694.2808315660823</c:v>
+                  <c:v>2694.3828943481803</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>2744.8492563179516</c:v>
+                  <c:v>2744.6787706078194</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>2756.4514910659673</c:v>
+                  <c:v>2756.0921308317684</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>2756.4514910659673</c:v>
+                  <c:v>2756.0921308317684</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>2756.4514910659673</c:v>
+                  <c:v>2756.0921308317684</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>2756.4514910659673</c:v>
+                  <c:v>2756.0921308317684</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>2756.4514910659673</c:v>
+                  <c:v>2756.0921308317684</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>2756.0921308317684</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4860,11 +4892,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="510286464"/>
-        <c:axId val="533717760"/>
+        <c:axId val="595688064"/>
+        <c:axId val="655438208"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="510286464"/>
+        <c:axId val="595688064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4907,14 +4939,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="533717760"/>
+        <c:crossAx val="655438208"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="533717760"/>
+        <c:axId val="655438208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4963,7 +4995,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="510286464"/>
+        <c:crossAx val="595688064"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5427,7 +5459,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF108"/>
+  <dimension ref="A1:AF109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -9559,7 +9591,7 @@
         <v>1.58121</v>
       </c>
       <c r="C99" s="20">
-        <v>1.0711721033591723</v>
+        <v>1.0709083815925535</v>
       </c>
       <c r="D99" s="21">
         <v>0</v>
@@ -9874,7 +9906,7 @@
         <v>1.87002</v>
       </c>
       <c r="C108" s="20">
-        <v>1.1261140396413394</v>
+        <v>1.1257628092540124</v>
       </c>
       <c r="D108" s="21">
         <v>0</v>
@@ -9898,6 +9930,41 @@
         <v>1706.083819284846</v>
       </c>
       <c r="K108" s="21">
+        <v>5934.4066689137917</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="12.75">
+      <c r="A109" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B109" s="25">
+        <v>1.87721</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.1334752732368041</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>4228.3228496289457</v>
+      </c>
+      <c r="I109" s="22">
+        <v>5934.4066689137917</v>
+      </c>
+      <c r="J109" s="22">
+        <v>1706.083819284846</v>
+      </c>
+      <c r="K109" s="21">
         <v>5934.4066689137917</v>
       </c>
     </row>
@@ -9919,7 +9986,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF96"/>
+  <dimension ref="A1:AF97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -9954,13 +10021,13 @@
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>20</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>22</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -10077,7 +10144,7 @@
         <v>16</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="V4" s="11" t="s">
         <v>18</v>
@@ -13509,19 +13576,19 @@
         <v>1.58121</v>
       </c>
       <c r="C87" s="20">
-        <v>1.1746116400000002</v>
+        <v>1.1721302800000002</v>
       </c>
       <c r="D87" s="21">
-        <v>-630.22745799999973</v>
+        <v>-634.07356599999969</v>
       </c>
       <c r="E87" s="22">
-        <v>-398.57290176510378</v>
+        <v>-401.00528456055787</v>
       </c>
       <c r="F87" s="22">
-        <v>1282.1849123718916</v>
+        <v>1279.7525295764376</v>
       </c>
       <c r="G87" s="22">
-        <v>2027.4036052915587</v>
+        <v>2023.557497291559</v>
       </c>
       <c r="H87" s="22">
         <v>6898.9353000000046</v>
@@ -13533,7 +13600,7 @@
         <v>2761.1841136018083</v>
       </c>
       <c r="K87" s="21">
-        <v>7632.715808310254</v>
+        <v>7636.5619163102547</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="12.75">
@@ -13553,22 +13620,22 @@
         <v>-326.83393866334842</v>
       </c>
       <c r="F88" s="22">
-        <v>955.35097370854328</v>
+        <v>952.91859091308925</v>
       </c>
       <c r="G88" s="22">
-        <v>1474.068338393334</v>
+        <v>1470.3152690352604</v>
       </c>
       <c r="H88" s="22">
         <v>6898.9353000000046</v>
       </c>
       <c r="I88" s="22">
-        <v>9611.0758407035883</v>
+        <v>9611.168879345516</v>
       </c>
       <c r="J88" s="22">
-        <v>2712.1405407035836</v>
+        <v>2712.2335793455113</v>
       </c>
       <c r="K88" s="21">
-        <v>8137.0075023102545</v>
+        <v>8140.8536103102551</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="12.75">
@@ -13588,22 +13655,22 @@
         <v>-245.88383759950912</v>
       </c>
       <c r="F89" s="22">
-        <v>709.46713610903419</v>
+        <v>707.03475331358015</v>
       </c>
       <c r="G89" s="22">
-        <v>1050.742112591563</v>
+        <v>1047.1396807000117</v>
       </c>
       <c r="H89" s="22">
         <v>6898.9353000000046</v>
       </c>
       <c r="I89" s="22">
-        <v>9551.9109549018176</v>
+        <v>9552.1546310102676</v>
       </c>
       <c r="J89" s="22">
-        <v>2652.975654901813</v>
+        <v>2653.219331010263</v>
       </c>
       <c r="K89" s="21">
-        <v>8501.1688423102551</v>
+        <v>8505.0149503102566</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="12.75">
@@ -13623,22 +13690,22 @@
         <v>-258.16481793081152</v>
       </c>
       <c r="F90" s="22">
-        <v>451.30231817822266</v>
+        <v>448.86993538276863</v>
       </c>
       <c r="G90" s="22">
-        <v>694.66709325582929</v>
+        <v>690.92304803792661</v>
       </c>
       <c r="H90" s="22">
         <v>6898.9353000000046</v>
       </c>
       <c r="I90" s="22">
-        <v>9593.2161315660869</v>
+        <v>9593.318194348185</v>
       </c>
       <c r="J90" s="22">
-        <v>2694.2808315660823</v>
+        <v>2694.3828943481803</v>
       </c>
       <c r="K90" s="21">
-        <v>8898.5490383102569</v>
+        <v>8902.3951463102585</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="12.75">
@@ -13658,22 +13725,22 @@
         <v>-301.88525767577124</v>
       </c>
       <c r="F91" s="22">
-        <v>149.41706050245142</v>
+        <v>146.98467770699739</v>
       </c>
       <c r="G91" s="22">
-        <v>246.73239200769802</v>
+        <v>242.71579829756479</v>
       </c>
       <c r="H91" s="22">
         <v>6898.9353000000046</v>
       </c>
       <c r="I91" s="22">
-        <v>9643.7845563179562</v>
+        <v>9643.614070607824</v>
       </c>
       <c r="J91" s="22">
-        <v>2744.8492563179516</v>
+        <v>2744.6787706078194</v>
       </c>
       <c r="K91" s="21">
-        <v>9397.0521643102584</v>
+        <v>9400.8982723102599</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="12.75">
@@ -13687,10 +13754,10 @@
         <v>1.3976433199999996</v>
       </c>
       <c r="D92" s="21">
-        <v>-258.33462675571337</v>
+        <v>-254.12915852151312</v>
       </c>
       <c r="E92" s="22">
-        <v>-149.41706050245142</v>
+        <v>-146.98467770699739</v>
       </c>
       <c r="F92" s="22">
         <v>0</v>
@@ -13702,13 +13769,13 @@
         <v>6898.9353000000046</v>
       </c>
       <c r="I92" s="22">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
       </c>
       <c r="J92" s="22">
-        <v>2756.4514910659673</v>
+        <v>2756.0921308317684</v>
       </c>
       <c r="K92" s="21">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="12.75">
@@ -13737,13 +13804,13 @@
         <v>6898.9353000000046</v>
       </c>
       <c r="I93" s="22">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
       </c>
       <c r="J93" s="22">
-        <v>2756.4514910659673</v>
+        <v>2756.0921308317684</v>
       </c>
       <c r="K93" s="21">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="12.75">
@@ -13772,13 +13839,13 @@
         <v>6898.9353000000046</v>
       </c>
       <c r="I94" s="22">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
       </c>
       <c r="J94" s="22">
-        <v>2756.4514910659673</v>
+        <v>2756.0921308317684</v>
       </c>
       <c r="K94" s="21">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="12.75">
@@ -13807,13 +13874,13 @@
         <v>6898.9353000000046</v>
       </c>
       <c r="I95" s="22">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
       </c>
       <c r="J95" s="22">
-        <v>2756.4514910659673</v>
+        <v>2756.0921308317684</v>
       </c>
       <c r="K95" s="21">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="12.75">
@@ -13824,7 +13891,7 @@
         <v>1.87002</v>
       </c>
       <c r="C96" s="20">
-        <v>1.6436552000000013</v>
+        <v>1.6419015200000018</v>
       </c>
       <c r="D96" s="21">
         <v>0</v>
@@ -13842,13 +13909,48 @@
         <v>6898.9353000000046</v>
       </c>
       <c r="I96" s="22">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
       </c>
       <c r="J96" s="22">
-        <v>2756.4514910659673</v>
+        <v>2756.0921308317684</v>
       </c>
       <c r="K96" s="21">
-        <v>9655.3867910659719</v>
+        <v>9655.027430831773</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="12.75">
+      <c r="A97" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B97" s="25">
+        <v>1.87721</v>
+      </c>
+      <c r="C97" s="20">
+        <v>1.6746592000000005</v>
+      </c>
+      <c r="D97" s="21">
+        <v>0</v>
+      </c>
+      <c r="E97" s="22">
+        <v>0</v>
+      </c>
+      <c r="F97" s="22">
+        <v>0</v>
+      </c>
+      <c r="G97" s="22">
+        <v>0</v>
+      </c>
+      <c r="H97" s="22">
+        <v>6898.9353000000046</v>
+      </c>
+      <c r="I97" s="22">
+        <v>9655.027430831773</v>
+      </c>
+      <c r="J97" s="22">
+        <v>2756.0921308317684</v>
+      </c>
+      <c r="K97" s="21">
+        <v>9655.027430831773</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/AIindex/AIinduindexmodel2cn.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel2cn.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -109,12 +109,16 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>MA250</t>
+    <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>绝对收益率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>人工智能产业指数</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>MA250</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -715,7 +719,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1033,6 +1037,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1042,7 +1049,7 @@
               <c:f>'模型二 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -1359,6 +1366,9 @@
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>4228.3228496289457</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
               </c:numCache>
@@ -1402,7 +1412,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1720,6 +1730,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1729,7 +1742,7 @@
               <c:f>'模型二 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="1">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -2043,6 +2056,9 @@
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>5934.4066689137917</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
               </c:numCache>
@@ -2086,7 +2102,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2404,6 +2420,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2413,7 +2432,7 @@
               <c:f>'模型二 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2730,6 +2749,9 @@
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>1706.083819284846</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
               </c:numCache>
@@ -2752,11 +2774,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="316529280"/>
-        <c:axId val="403558784"/>
+        <c:axId val="412200960"/>
+        <c:axId val="493124992"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="316529280"/>
+        <c:axId val="412200960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2799,14 +2821,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="403558784"/>
+        <c:crossAx val="493124992"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="403558784"/>
+        <c:axId val="493124992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2855,7 +2877,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="316529280"/>
+        <c:crossAx val="412200960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3068,7 +3090,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3350,6 +3372,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3359,7 +3384,7 @@
               <c:f>'模型二 (1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3640,6 +3665,9 @@
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
                 <c:pt idx="93">
+                  <c:v>6898.9353000000046</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
               </c:numCache>
@@ -3683,7 +3711,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3965,6 +3993,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3974,7 +4005,7 @@
               <c:f>'模型二 (1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4255,6 +4286,9 @@
                   <c:v>9655.027430831773</c:v>
                 </c:pt>
                 <c:pt idx="93">
+                  <c:v>9655.027430831773</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>9655.027430831773</c:v>
                 </c:pt>
               </c:numCache>
@@ -4298,7 +4332,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4580,6 +4614,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4589,7 +4626,7 @@
               <c:f>'模型二 (1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4870,6 +4907,9 @@
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
                 <c:pt idx="93">
+                  <c:v>2756.0921308317684</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
               </c:numCache>
@@ -4892,11 +4932,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="595688064"/>
-        <c:axId val="655438208"/>
+        <c:axId val="559795200"/>
+        <c:axId val="610740096"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="595688064"/>
+        <c:axId val="559795200"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4939,14 +4979,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="655438208"/>
+        <c:crossAx val="610740096"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="655438208"/>
+        <c:axId val="610740096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4995,7 +5035,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="595688064"/>
+        <c:crossAx val="559795200"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5103,7 +5143,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5146,7 +5186,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5459,7 +5499,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF109"/>
+  <dimension ref="A1:AF110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -9968,6 +10008,41 @@
         <v>5934.4066689137917</v>
       </c>
     </row>
+    <row r="110" spans="1:11" ht="12.75">
+      <c r="A110" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.0358800000000001</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.1419948172142516</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>4228.3228496289457</v>
+      </c>
+      <c r="I110" s="22">
+        <v>5934.4066689137917</v>
+      </c>
+      <c r="J110" s="22">
+        <v>1706.083819284846</v>
+      </c>
+      <c r="K110" s="21">
+        <v>5934.4066689137917</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -9986,7 +10061,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF97"/>
+  <dimension ref="A1:AF98"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -10021,13 +10096,13 @@
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -10144,7 +10219,7 @@
         <v>16</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="V4" s="11" t="s">
         <v>18</v>
@@ -13950,6 +14025,41 @@
         <v>2756.0921308317684</v>
       </c>
       <c r="K97" s="21">
+        <v>9655.027430831773</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="12.75">
+      <c r="A98" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B98" s="25">
+        <v>2.0358800000000001</v>
+      </c>
+      <c r="C98" s="20">
+        <v>1.7296812799999999</v>
+      </c>
+      <c r="D98" s="21">
+        <v>0</v>
+      </c>
+      <c r="E98" s="22">
+        <v>0</v>
+      </c>
+      <c r="F98" s="22">
+        <v>0</v>
+      </c>
+      <c r="G98" s="22">
+        <v>0</v>
+      </c>
+      <c r="H98" s="22">
+        <v>6898.9353000000046</v>
+      </c>
+      <c r="I98" s="22">
+        <v>9655.027430831773</v>
+      </c>
+      <c r="J98" s="22">
+        <v>2756.0921308317684</v>
+      </c>
+      <c r="K98" s="21">
         <v>9655.027430831773</v>
       </c>
     </row>

--- a/lai/valuationquan/AIindex/AIinduindexmodel2cn.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel2cn.xlsx
@@ -719,7 +719,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1040,6 +1040,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1049,7 +1052,7 @@
               <c:f>'模型二 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -1369,6 +1372,9 @@
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>4228.3228496289457</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
               </c:numCache>
@@ -1412,7 +1418,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1733,6 +1739,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1742,7 +1751,7 @@
               <c:f>'模型二 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="1">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -2059,6 +2068,9 @@
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>5934.4066689137917</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
               </c:numCache>
@@ -2102,7 +2114,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2423,6 +2435,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2432,7 +2447,7 @@
               <c:f>'模型二 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2752,6 +2767,9 @@
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>1706.083819284846</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
               </c:numCache>
@@ -2774,11 +2792,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="412200960"/>
-        <c:axId val="493124992"/>
+        <c:axId val="77523968"/>
+        <c:axId val="77542912"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="412200960"/>
+        <c:axId val="77523968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2821,14 +2839,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="493124992"/>
+        <c:crossAx val="77542912"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="493124992"/>
+        <c:axId val="77542912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2877,7 +2895,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="412200960"/>
+        <c:crossAx val="77523968"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3090,7 +3108,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3375,6 +3393,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3384,7 +3405,7 @@
               <c:f>'模型二 (1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3668,6 +3689,9 @@
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
                 <c:pt idx="94">
+                  <c:v>6898.9353000000046</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
               </c:numCache>
@@ -3711,7 +3735,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3996,6 +4020,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4005,7 +4032,7 @@
               <c:f>'模型二 (1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4289,6 +4316,9 @@
                   <c:v>9655.027430831773</c:v>
                 </c:pt>
                 <c:pt idx="94">
+                  <c:v>9655.027430831773</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>9655.027430831773</c:v>
                 </c:pt>
               </c:numCache>
@@ -4332,7 +4362,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4617,6 +4647,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4626,7 +4659,7 @@
               <c:f>'模型二 (1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4910,6 +4943,9 @@
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
                 <c:pt idx="94">
+                  <c:v>2756.0921308317684</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
               </c:numCache>
@@ -4932,11 +4968,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="559795200"/>
-        <c:axId val="610740096"/>
+        <c:axId val="397589888"/>
+        <c:axId val="423730176"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="559795200"/>
+        <c:axId val="397589888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4979,14 +5015,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="610740096"/>
+        <c:crossAx val="423730176"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="610740096"/>
+        <c:axId val="423730176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5035,7 +5071,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559795200"/>
+        <c:crossAx val="397589888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5143,7 +5179,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5186,7 +5222,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5499,7 +5535,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF110"/>
+  <dimension ref="A1:AF111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -10043,6 +10079,41 @@
         <v>5934.4066689137917</v>
       </c>
     </row>
+    <row r="111" spans="1:11" ht="12.75">
+      <c r="A111" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B111" s="25">
+        <v>2.0871900000000001</v>
+      </c>
+      <c r="C111" s="20">
+        <v>1.1482512499999991</v>
+      </c>
+      <c r="D111" s="21">
+        <v>0</v>
+      </c>
+      <c r="E111" s="22">
+        <v>0</v>
+      </c>
+      <c r="F111" s="22">
+        <v>0</v>
+      </c>
+      <c r="G111" s="22">
+        <v>0</v>
+      </c>
+      <c r="H111" s="22">
+        <v>4228.3228496289457</v>
+      </c>
+      <c r="I111" s="22">
+        <v>5934.4066689137917</v>
+      </c>
+      <c r="J111" s="22">
+        <v>1706.083819284846</v>
+      </c>
+      <c r="K111" s="21">
+        <v>5934.4066689137917</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -10061,7 +10132,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF98"/>
+  <dimension ref="A1:AF99"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14063,6 +14134,41 @@
         <v>9655.027430831773</v>
       </c>
     </row>
+    <row r="99" spans="1:11" ht="12.75">
+      <c r="A99" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B99" s="25">
+        <v>2.0871900000000001</v>
+      </c>
+      <c r="C99" s="20">
+        <v>1.7625963599999996</v>
+      </c>
+      <c r="D99" s="21">
+        <v>0</v>
+      </c>
+      <c r="E99" s="22">
+        <v>0</v>
+      </c>
+      <c r="F99" s="22">
+        <v>0</v>
+      </c>
+      <c r="G99" s="22">
+        <v>0</v>
+      </c>
+      <c r="H99" s="22">
+        <v>6898.9353000000046</v>
+      </c>
+      <c r="I99" s="22">
+        <v>9655.027430831773</v>
+      </c>
+      <c r="J99" s="22">
+        <v>2756.0921308317684</v>
+      </c>
+      <c r="K99" s="21">
+        <v>9655.027430831773</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">

--- a/lai/valuationquan/AIindex/AIinduindexmodel2cn.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel2cn.xlsx
@@ -719,7 +719,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1043,6 +1043,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1052,7 +1055,7 @@
               <c:f>'模型二 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -1375,6 +1378,9 @@
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>4228.3228496289457</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
               </c:numCache>
@@ -1418,7 +1424,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1742,6 +1748,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1751,7 +1760,7 @@
               <c:f>'模型二 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="1">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -2071,6 +2080,9 @@
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>5934.4066689137917</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
               </c:numCache>
@@ -2114,7 +2126,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2438,6 +2450,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2447,7 +2462,7 @@
               <c:f>'模型二 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2770,6 +2785,9 @@
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>1706.083819284846</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
               </c:numCache>
@@ -2792,11 +2810,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="77523968"/>
-        <c:axId val="77542912"/>
+        <c:axId val="385507328"/>
+        <c:axId val="385510400"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="77523968"/>
+        <c:axId val="385507328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2839,14 +2857,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77542912"/>
+        <c:crossAx val="385510400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="77542912"/>
+        <c:axId val="385510400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2895,7 +2913,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77523968"/>
+        <c:crossAx val="385507328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3108,7 +3126,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3396,6 +3414,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3405,7 +3426,7 @@
               <c:f>'模型二 (1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3692,6 +3713,9 @@
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>6898.9353000000046</c:v>
+                </c:pt>
+                <c:pt idx="96">
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
               </c:numCache>
@@ -3735,7 +3759,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4023,6 +4047,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4032,7 +4059,7 @@
               <c:f>'模型二 (1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4319,6 +4346,9 @@
                   <c:v>9655.027430831773</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>9655.027430831773</c:v>
+                </c:pt>
+                <c:pt idx="96">
                   <c:v>9655.027430831773</c:v>
                 </c:pt>
               </c:numCache>
@@ -4362,7 +4392,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4650,6 +4680,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4659,7 +4692,7 @@
               <c:f>'模型二 (1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4946,6 +4979,9 @@
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>2756.0921308317684</c:v>
+                </c:pt>
+                <c:pt idx="96">
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
               </c:numCache>
@@ -4968,11 +5004,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="397589888"/>
-        <c:axId val="423730176"/>
+        <c:axId val="417242496"/>
+        <c:axId val="417354880"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="397589888"/>
+        <c:axId val="417242496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5015,14 +5051,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="423730176"/>
+        <c:crossAx val="417354880"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="423730176"/>
+        <c:axId val="417354880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5071,7 +5107,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="397589888"/>
+        <c:crossAx val="417242496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5179,7 +5215,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5222,7 +5258,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5535,7 +5571,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF111"/>
+  <dimension ref="A1:AF112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -10114,6 +10150,41 @@
         <v>5934.4066689137917</v>
       </c>
     </row>
+    <row r="112" spans="1:11" ht="12.75">
+      <c r="A112" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B112" s="25">
+        <v>1.8343499999999999</v>
+      </c>
+      <c r="C112" s="20">
+        <v>1.1561043221110083</v>
+      </c>
+      <c r="D112" s="21">
+        <v>0</v>
+      </c>
+      <c r="E112" s="22">
+        <v>0</v>
+      </c>
+      <c r="F112" s="22">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>4228.3228496289457</v>
+      </c>
+      <c r="I112" s="22">
+        <v>5934.4066689137917</v>
+      </c>
+      <c r="J112" s="22">
+        <v>1706.083819284846</v>
+      </c>
+      <c r="K112" s="21">
+        <v>5934.4066689137917</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -10132,7 +10203,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF99"/>
+  <dimension ref="A1:AF100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14169,6 +14240,41 @@
         <v>9655.027430831773</v>
       </c>
     </row>
+    <row r="100" spans="1:11" ht="12.75">
+      <c r="A100" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B100" s="25">
+        <v>1.8343499999999999</v>
+      </c>
+      <c r="C100" s="20">
+        <v>1.7862818</v>
+      </c>
+      <c r="D100" s="21">
+        <v>0</v>
+      </c>
+      <c r="E100" s="22">
+        <v>0</v>
+      </c>
+      <c r="F100" s="22">
+        <v>0</v>
+      </c>
+      <c r="G100" s="22">
+        <v>0</v>
+      </c>
+      <c r="H100" s="22">
+        <v>6898.9353000000046</v>
+      </c>
+      <c r="I100" s="22">
+        <v>9655.027430831773</v>
+      </c>
+      <c r="J100" s="22">
+        <v>2756.0921308317684</v>
+      </c>
+      <c r="K100" s="21">
+        <v>9655.027430831773</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">

--- a/lai/valuationquan/AIindex/AIinduindexmodel2cn.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel2cn.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -119,6 +119,10 @@
   <si>
     <t>MA250</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：元</t>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -719,7 +723,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1046,6 +1050,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1055,7 +1062,7 @@
               <c:f>'模型二 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -1381,6 +1388,9 @@
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>4228.3228496289457</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
               </c:numCache>
@@ -1424,7 +1434,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1751,6 +1761,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1760,7 +1773,7 @@
               <c:f>'模型二 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="1">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -2083,6 +2096,9 @@
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>5934.4066689137917</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
               </c:numCache>
@@ -2126,7 +2142,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2453,6 +2469,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2462,7 +2481,7 @@
               <c:f>'模型二 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2788,6 +2807,9 @@
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>1706.083819284846</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
               </c:numCache>
@@ -2810,11 +2832,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="385507328"/>
-        <c:axId val="385510400"/>
+        <c:axId val="102150144"/>
+        <c:axId val="102151680"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="385507328"/>
+        <c:axId val="102150144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2857,14 +2879,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="385510400"/>
+        <c:crossAx val="102151680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="385510400"/>
+        <c:axId val="102151680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2913,7 +2935,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="385507328"/>
+        <c:crossAx val="102150144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3126,7 +3148,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3417,6 +3439,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3426,7 +3451,7 @@
               <c:f>'模型二 (1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3716,6 +3741,9 @@
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
                 <c:pt idx="96">
+                  <c:v>6898.9353000000046</c:v>
+                </c:pt>
+                <c:pt idx="97">
                   <c:v>6898.9353000000046</c:v>
                 </c:pt>
               </c:numCache>
@@ -3759,7 +3787,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4050,6 +4078,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4059,7 +4090,7 @@
               <c:f>'模型二 (1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4349,6 +4380,9 @@
                   <c:v>9655.027430831773</c:v>
                 </c:pt>
                 <c:pt idx="96">
+                  <c:v>9655.027430831773</c:v>
+                </c:pt>
+                <c:pt idx="97">
                   <c:v>9655.027430831773</c:v>
                 </c:pt>
               </c:numCache>
@@ -4392,7 +4426,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4683,6 +4717,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4692,7 +4729,7 @@
               <c:f>'模型二 (1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4982,6 +5019,9 @@
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
                 <c:pt idx="96">
+                  <c:v>2756.0921308317684</c:v>
+                </c:pt>
+                <c:pt idx="97">
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
               </c:numCache>
@@ -5004,11 +5044,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="417242496"/>
-        <c:axId val="417354880"/>
+        <c:axId val="117822592"/>
+        <c:axId val="117824128"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="417242496"/>
+        <c:axId val="117822592"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5051,14 +5091,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="417354880"/>
+        <c:crossAx val="117824128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="417354880"/>
+        <c:axId val="117824128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5107,7 +5147,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="417242496"/>
+        <c:crossAx val="117822592"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5215,7 +5255,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5258,7 +5298,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5571,7 +5611,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF112"/>
+  <dimension ref="A1:AF113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -10185,6 +10225,41 @@
         <v>5934.4066689137917</v>
       </c>
     </row>
+    <row r="113" spans="1:11" ht="12.75">
+      <c r="A113" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B113" s="25">
+        <v>1.9266700000000001</v>
+      </c>
+      <c r="C113" s="20">
+        <v>1.1626960820559045</v>
+      </c>
+      <c r="D113" s="21">
+        <v>0</v>
+      </c>
+      <c r="E113" s="22">
+        <v>0</v>
+      </c>
+      <c r="F113" s="22">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>4228.3228496289457</v>
+      </c>
+      <c r="I113" s="22">
+        <v>5934.4066689137917</v>
+      </c>
+      <c r="J113" s="22">
+        <v>1706.083819284846</v>
+      </c>
+      <c r="K113" s="21">
+        <v>5934.4066689137917</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -10203,7 +10278,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF100"/>
+  <dimension ref="A1:AF101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -10294,7 +10369,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -14272,6 +14347,41 @@
         <v>2756.0921308317684</v>
       </c>
       <c r="K100" s="21">
+        <v>9655.027430831773</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="12.75">
+      <c r="A101" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B101" s="25">
+        <v>1.9266700000000001</v>
+      </c>
+      <c r="C101" s="20">
+        <v>1.8123291999999998</v>
+      </c>
+      <c r="D101" s="21">
+        <v>0</v>
+      </c>
+      <c r="E101" s="22">
+        <v>0</v>
+      </c>
+      <c r="F101" s="22">
+        <v>0</v>
+      </c>
+      <c r="G101" s="22">
+        <v>0</v>
+      </c>
+      <c r="H101" s="22">
+        <v>6898.9353000000046</v>
+      </c>
+      <c r="I101" s="22">
+        <v>9655.027430831773</v>
+      </c>
+      <c r="J101" s="22">
+        <v>2756.0921308317684</v>
+      </c>
+      <c r="K101" s="21">
         <v>9655.027430831773</v>
       </c>
     </row>

--- a/lai/valuationquan/AIindex/AIinduindexmodel2cn.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel2cn.xlsx
@@ -723,7 +723,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1053,6 +1053,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1062,7 +1065,7 @@
               <c:f>'模型二 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -1391,6 +1394,9 @@
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>4228.3228496289457</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>4228.3228496289457</c:v>
                 </c:pt>
               </c:numCache>
@@ -1434,7 +1440,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1764,6 +1770,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1773,7 +1782,7 @@
               <c:f>'模型二 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="1">
                   <c:v>27.550142857142728</c:v>
                 </c:pt>
@@ -2099,6 +2108,9 @@
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>5934.4066689137917</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>5934.4066689137917</c:v>
                 </c:pt>
               </c:numCache>
@@ -2142,7 +2154,7 @@
               <c:f>'模型二 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2472,6 +2484,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2481,7 +2496,7 @@
               <c:f>'模型二 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2810,6 +2825,9 @@
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>1706.083819284846</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>1706.083819284846</c:v>
                 </c:pt>
               </c:numCache>
@@ -2832,11 +2850,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="102150144"/>
-        <c:axId val="102151680"/>
+        <c:axId val="94116864"/>
+        <c:axId val="99717888"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="102150144"/>
+        <c:axId val="94116864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2879,14 +2897,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="102151680"/>
+        <c:crossAx val="99717888"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="102151680"/>
+        <c:axId val="99717888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2935,7 +2953,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="102150144"/>
+        <c:crossAx val="94116864"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3148,7 +3166,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3442,6 +3460,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3451,7 +3472,7 @@
               <c:f>'模型二 (1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3745,6 +3766,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>6898.9353000000046</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>6917.0073080000038</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3787,7 +3811,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4081,6 +4105,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4090,7 +4117,7 @@
               <c:f>'模型二 (1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4384,6 +4411,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>9655.027430831773</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>9673.0994388317722</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4426,7 +4456,7 @@
               <c:f>'模型二 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4720,6 +4750,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4729,7 +4762,7 @@
               <c:f>'模型二 (1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5022,6 +5055,9 @@
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
                 <c:pt idx="97">
+                  <c:v>2756.0921308317684</c:v>
+                </c:pt>
+                <c:pt idx="98">
                   <c:v>2756.0921308317684</c:v>
                 </c:pt>
               </c:numCache>
@@ -5044,11 +5080,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="117822592"/>
-        <c:axId val="117824128"/>
+        <c:axId val="390303104"/>
+        <c:axId val="399529088"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="117822592"/>
+        <c:axId val="390303104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5091,14 +5127,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="117824128"/>
+        <c:crossAx val="399529088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="117824128"/>
+        <c:axId val="399529088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5147,7 +5183,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="117822592"/>
+        <c:crossAx val="390303104"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5255,7 +5291,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5298,7 +5334,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5611,7 +5647,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF113"/>
+  <dimension ref="A1:AF114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -10260,6 +10296,41 @@
         <v>5934.4066689137917</v>
       </c>
     </row>
+    <row r="114" spans="1:11" ht="12.75">
+      <c r="A114" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B114" s="25">
+        <v>1.8331300000000001</v>
+      </c>
+      <c r="C114" s="20">
+        <v>1.1691162343470469</v>
+      </c>
+      <c r="D114" s="21">
+        <v>0</v>
+      </c>
+      <c r="E114" s="22">
+        <v>0</v>
+      </c>
+      <c r="F114" s="22">
+        <v>0</v>
+      </c>
+      <c r="G114" s="22">
+        <v>0</v>
+      </c>
+      <c r="H114" s="22">
+        <v>4228.3228496289457</v>
+      </c>
+      <c r="I114" s="22">
+        <v>5934.4066689137917</v>
+      </c>
+      <c r="J114" s="22">
+        <v>1706.083819284846</v>
+      </c>
+      <c r="K114" s="21">
+        <v>5934.4066689137917</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -10275,10 +10346,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet2">
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
-  <dimension ref="A1:AF101"/>
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:AF102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -14385,6 +14454,41 @@
         <v>9655.027430831773</v>
       </c>
     </row>
+    <row r="102" spans="1:11" ht="12.75">
+      <c r="A102" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B102" s="25">
+        <v>1.8331300000000001</v>
+      </c>
+      <c r="C102" s="20">
+        <v>1.8447893599999998</v>
+      </c>
+      <c r="D102" s="21">
+        <v>18.072007999999496</v>
+      </c>
+      <c r="E102" s="22">
+        <v>9.858552312165255</v>
+      </c>
+      <c r="F102" s="22">
+        <v>9.858552312165255</v>
+      </c>
+      <c r="G102" s="22">
+        <v>18.072007999999496</v>
+      </c>
+      <c r="H102" s="22">
+        <v>6917.0073080000038</v>
+      </c>
+      <c r="I102" s="22">
+        <v>9673.0994388317722</v>
+      </c>
+      <c r="J102" s="22">
+        <v>2756.0921308317684</v>
+      </c>
+      <c r="K102" s="21">
+        <v>9655.027430831773</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
